--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.45077995717023</v>
+        <v>4.948251743040162</v>
       </c>
       <c r="D2" t="n">
-        <v>30.91752923146331</v>
+        <v>5.024098500112787</v>
       </c>
       <c r="E2" t="n">
-        <v>17.50717789954138</v>
+        <v>2.844916408675475</v>
       </c>
       <c r="F2" t="n">
-        <v>14.82422510539079</v>
+        <v>2.408936579626003</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.20037878244409</v>
+        <v>2.145061552147164</v>
       </c>
       <c r="D3" t="n">
-        <v>27.25675422377773</v>
+        <v>4.429222561363881</v>
       </c>
       <c r="E3" t="n">
-        <v>17.50717789954138</v>
+        <v>2.844916408675475</v>
       </c>
       <c r="F3" t="n">
-        <v>14.82422510539079</v>
+        <v>2.408936579626003</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.70511759152997</v>
+        <v>9.539581608623621</v>
       </c>
       <c r="D4" t="n">
-        <v>52.78816069986416</v>
+        <v>8.578076113727928</v>
       </c>
       <c r="E4" t="n">
-        <v>17.50717789954138</v>
+        <v>2.844916408675475</v>
       </c>
       <c r="F4" t="n">
-        <v>14.82422510539079</v>
+        <v>2.408936579626003</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.68454363267113</v>
+        <v>7.748738340309059</v>
       </c>
       <c r="D5" t="n">
-        <v>38.46807259304372</v>
+        <v>6.251061796369605</v>
       </c>
       <c r="E5" t="n">
-        <v>17.50717789954138</v>
+        <v>2.844916408675475</v>
       </c>
       <c r="F5" t="n">
-        <v>14.82422510539079</v>
+        <v>2.408936579626003</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.48166760689537</v>
+        <v>5.440770986120498</v>
       </c>
       <c r="D6" t="n">
-        <v>33.01055317882592</v>
+        <v>5.364214891559212</v>
       </c>
       <c r="E6" t="n">
-        <v>17.50717789954138</v>
+        <v>2.844916408675475</v>
       </c>
       <c r="F6" t="n">
-        <v>14.82422510539079</v>
+        <v>2.408936579626003</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.79139768448814</v>
+        <v>4.841102123729322</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69760452876442</v>
+        <v>5.800860735924218</v>
       </c>
       <c r="E7" t="n">
-        <v>17.50717789954138</v>
+        <v>2.844916408675475</v>
       </c>
       <c r="F7" t="n">
-        <v>14.82422510539079</v>
+        <v>2.408936579626003</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.03652907744939</v>
+        <v>2.768435975085527</v>
       </c>
       <c r="D8" t="n">
-        <v>18.03592534271941</v>
+        <v>2.930837868191905</v>
       </c>
       <c r="E8" t="n">
-        <v>17.50717789954138</v>
+        <v>2.844916408675475</v>
       </c>
       <c r="F8" t="n">
-        <v>14.82422510539079</v>
+        <v>2.408936579626003</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>60.73163991258802</v>
+        <v>9.868891485795553</v>
       </c>
       <c r="D9" t="n">
-        <v>59.80085856847032</v>
+        <v>9.717639517376426</v>
       </c>
       <c r="E9" t="n">
-        <v>17.50717789954138</v>
+        <v>2.844916408675475</v>
       </c>
       <c r="F9" t="n">
-        <v>14.82422510539079</v>
+        <v>2.408936579626003</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.429507706206227</v>
+        <v>1.532295002258512</v>
       </c>
       <c r="D10" t="n">
-        <v>9.454596287587282</v>
+        <v>1.536371896732933</v>
       </c>
       <c r="E10" t="n">
-        <v>17.50717789954138</v>
+        <v>2.844916408675475</v>
       </c>
       <c r="F10" t="n">
-        <v>14.82422510539079</v>
+        <v>2.408936579626003</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.29856416021594</v>
+        <v>8.98601667603509</v>
       </c>
       <c r="D11" t="n">
-        <v>54.17068268056594</v>
+        <v>8.802735935591965</v>
       </c>
       <c r="E11" t="n">
-        <v>17.50717789954138</v>
+        <v>2.844916408675475</v>
       </c>
       <c r="F11" t="n">
-        <v>14.82422510539079</v>
+        <v>2.408936579626003</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.43647932530837</v>
+        <v>4.295927890362609</v>
       </c>
       <c r="D12" t="n">
-        <v>25.78655960247211</v>
+        <v>4.190315935401718</v>
       </c>
       <c r="E12" t="n">
-        <v>17.50717789954138</v>
+        <v>2.844916408675475</v>
       </c>
       <c r="F12" t="n">
-        <v>14.82422510539079</v>
+        <v>2.408936579626003</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
